--- a/NBFC-MF/Borrowers/Sanarei_Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Sanarei_Group_Weekly.xlsx
@@ -1800,42 +1800,44 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B13" s="23">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>12600</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>1414.953508840923</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="4"/>
+        <v>11185.046491159077</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="5"/>
+        <v>59380.703111526433</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>120619.29688847356</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>75600</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1870,7 +1872,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>70565.749602685508</v>
+        <v>59380.703111526433</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1905,7 +1907,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>109434.25039731449</v>
+        <v>120619.29688847356</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Sanarei_Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Sanarei_Group_Weekly.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1837,42 +1837,44 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>63000</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B14" s="22">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H14" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>12600</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>1190.675854761952</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="4"/>
+        <v>11409.324145238048</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="5"/>
+        <v>47971.378966288386</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="2"/>
+        <v>132028.62103371162</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>59380.703111526433</v>
+        <v>47971.378966288386</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1907,7 +1909,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>120619.29688847356</v>
+        <v>132028.62103371162</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Sanarei_Group_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Sanarei_Group_Weekly.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>50400</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1874,42 +1874,44 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>47971.378966288386</v>
+        <v>36333.28004966757</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B15" s="23">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>12600</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>961.90108337918377</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="4"/>
+        <v>11638.098916620816</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="5"/>
+        <v>36333.28004966757</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>143666.71995033242</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>5</v>
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>132028.62103371162</v>
+        <v>143666.71995033242</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
